--- a/1.Training_model/supplementary/XenIdentifier Project Timeline.xlsx
+++ b/1.Training_model/supplementary/XenIdentifier Project Timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DeviceIdentifier\1.Training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6E1336-424F-4ED8-A860-6FFDCDCAF298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44094F06-DF23-42EE-9591-A51DBAB88183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
